--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484539_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484539_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3125</v>
+        <v>5.3213</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9938</v>
+        <v>3.7054</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3187</v>
+        <v>1.616</v>
       </c>
       <c r="G2" t="n">
         <v>0.5841</v>
@@ -610,13 +610,13 @@
         <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0047</v>
+        <v>0.0042</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3092</v>
+        <v>0.0208</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3139</v>
+        <v>-0.0166</v>
       </c>
       <c r="V2" t="n">
         <v>2.5339</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5049</v>
+        <v>5.2578</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1527</v>
+        <v>5.8808</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6478</v>
+        <v>-0.623</v>
       </c>
       <c r="G3" t="n">
         <v>2.054</v>
@@ -688,13 +688,13 @@
         <v>1.8326</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1554</v>
+        <v>-0.4025</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0279</v>
+        <v>-0.2997</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1276</v>
+        <v>-0.1028</v>
       </c>
       <c r="V3" t="n">
         <v>1.7738</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBANEZ</t>
+          <t>G. LOPEZ ABAD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9576</v>
+        <v>3.7198</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8012</v>
+        <v>2.2033</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1564</v>
+        <v>1.5165</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4857</v>
+        <v>1.9531</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7842</v>
+        <v>2.8444</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.2986</v>
+        <v>-0.8914</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8615</v>
+        <v>2.0924</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2942</v>
+        <v>2.5668</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4327</v>
+        <v>-0.4743</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3759</v>
+        <v>-0.1394</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.51</v>
+        <v>0.2777</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8659</v>
+        <v>-0.417</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.733</v>
+        <v>0.9163</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0158</v>
+        <v>1.8326</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8423</v>
+        <v>-0.4165</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1991</v>
+        <v>-0.2398</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6432</v>
+        <v>-0.1767</v>
       </c>
       <c r="V4" t="n">
-        <v>3.3627</v>
+        <v>1.267</v>
       </c>
       <c r="W4" t="n">
-        <v>3.4894</v>
+        <v>1.267</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. LOPEZ ABAD</t>
+          <t>A. ORTEGA IBANEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6951</v>
+        <v>3.2535</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2033</v>
+        <v>2.5678</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4918</v>
+        <v>0.6857</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9531</v>
+        <v>0.4857</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8444</v>
+        <v>1.7842</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8914</v>
+        <v>-1.2986</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0924</v>
+        <v>1.8615</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5668</v>
+        <v>2.2942</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4743</v>
+        <v>-0.4327</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1394</v>
+        <v>-1.3759</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2777</v>
+        <v>-0.51</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.417</v>
+        <v>-0.8659</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9163</v>
+        <v>-0.733</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8326</v>
+        <v>2.0158</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4413</v>
+        <v>0.1382</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2398</v>
+        <v>-0.0343</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2015</v>
+        <v>0.1725</v>
       </c>
       <c r="V5" t="n">
-        <v>1.267</v>
+        <v>3.3627</v>
       </c>
       <c r="W5" t="n">
-        <v>1.267</v>
+        <v>3.4894</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1267</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. BERENGUER CASCO</t>
+          <t>A. ORTEGA IBAÑEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0357</v>
+        <v>1.9005</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7308</v>
+        <v>1.9005</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3049</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2511</v>
+        <v>1.9005</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3503</v>
+        <v>0.6502</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0993</v>
+        <v>1.2502</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8636</v>
+        <v>1.9005</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1612</v>
+        <v>0.6502</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7024</v>
+        <v>1.2502</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6125</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1891</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8017</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3932</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0565</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4497</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1403</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4486</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBAÑEZ</t>
+          <t>M. BERENGUER CASCO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9005</v>
+        <v>1.5516</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9005</v>
+        <v>1.5935</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0.042</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9005</v>
+        <v>3.2511</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6502</v>
+        <v>3.3503</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2502</v>
+        <v>-0.0993</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9005</v>
+        <v>3.8636</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6502</v>
+        <v>3.1612</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2502</v>
+        <v>0.7024</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0.6125</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.1891</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.8017</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.1938</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.1029</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.1403</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.4486</v>
       </c>
     </row>
     <row r="8">
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. BERMEJO DORRONSORO</t>
+          <t>P. BAENA SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.172</v>
+        <v>-0.6131</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8892</v>
+        <v>-2.2864</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2828</v>
+        <v>1.6733</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3364</v>
+        <v>-0.9031</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1536</v>
+        <v>0.4783</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1828</v>
+        <v>-1.3813</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4035</v>
+        <v>-1.2355</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1701</v>
+        <v>0.5944</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5736</v>
+        <v>-1.8299</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9329</v>
+        <v>0.3324</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3237</v>
+        <v>-0.1161</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6092</v>
+        <v>0.4486</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9163</v>
+        <v>1.6493</v>
       </c>
       <c r="S10" t="n">
-        <v>0.291</v>
+        <v>-0.3164</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1086</v>
+        <v>-0.1346</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1824</v>
+        <v>-0.1818</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1267</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.4486</v>
+        <v>-0.1267</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. FRANCH RUIZ</t>
+          <t>J. BERMEJO DORRONSORO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5323</v>
+        <v>-1.3396</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0304</v>
+        <v>-1.0815</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5018</v>
+        <v>-0.2581</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.181</v>
+        <v>-1.3364</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9246</v>
+        <v>-0.1536</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2564</v>
+        <v>-1.1828</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2604</v>
+        <v>-0.4035</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6194</v>
+        <v>0.1701</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.641</v>
+        <v>-0.5736</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0793</v>
+        <v>-0.9329</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3053</v>
+        <v>-0.3237</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3846</v>
+        <v>-0.6092</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="S11" t="n">
-        <v>0.044</v>
+        <v>0.1235</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.092</v>
+        <v>-0.0837</v>
       </c>
       <c r="U11" t="n">
-        <v>0.136</v>
+        <v>0.2072</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.945</v>
+        <v>-0.1267</v>
       </c>
       <c r="W11" t="n">
         <v>0.3219</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.267</v>
+        <v>-0.4486</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. BAENA SANCHEZ</t>
+          <t>I. FRANCH RUIZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6825</v>
+        <v>-1.439</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9594</v>
+        <v>-0.8381</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2769</v>
+        <v>-0.6009</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9031</v>
+        <v>-1.181</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4783</v>
+        <v>-0.9246</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3813</v>
+        <v>-0.2564</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2355</v>
+        <v>-1.2604</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5944</v>
+        <v>-0.6194</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8299</v>
+        <v>-0.641</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3324</v>
+        <v>0.0793</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1161</v>
+        <v>-0.3053</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4486</v>
+        <v>0.3846</v>
       </c>
       <c r="P12" t="n">
-        <v>0.733</v>
+        <v>0.5498</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6493</v>
+        <v>0.5498</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3858</v>
+        <v>0.1373</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8077</v>
+        <v>0.1003</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5780999999999999</v>
+        <v>0.0369</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1267</v>
+        <v>-0.945</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1267</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7775</v>
+        <v>-3.0357</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8812</v>
+        <v>-2.1146</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8963</v>
+        <v>-0.9211</v>
       </c>
       <c r="G13" t="n">
         <v>-2.0981</v>
@@ -1468,13 +1468,13 @@
         <v>0.9163</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5876</v>
+        <v>0.3294</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2738</v>
+        <v>0.0404</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3138</v>
+        <v>0.289</v>
       </c>
       <c r="V13" t="n">
         <v>-1.267</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.9401</v>
+        <v>-5.5363</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2027</v>
+        <v>-0.7246</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.7374</v>
+        <v>-4.8117</v>
       </c>
       <c r="G14" t="n">
         <v>-1.0497</v>
@@ -1546,13 +1546,13 @@
         <v>1.0995</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9942</v>
+        <v>0.398</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8228</v>
+        <v>0.3009</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1714</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-5.0679</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-8.017300000000001</v>
+        <v>-7.4811</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.5415</v>
+        <v>-7.2531</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4757</v>
+        <v>-0.228</v>
       </c>
       <c r="G15" t="n">
         <v>-4.92</v>
@@ -1624,13 +1624,13 @@
         <v>0.733</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0814</v>
+        <v>-0.5452</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6056</v>
+        <v>-0.3171</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4759</v>
+        <v>-0.2281</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,22 +1657,22 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.910199999999998</v>
+        <v>3.1853</v>
       </c>
       <c r="E16" t="n">
-        <v>4.903499999999998</v>
+        <v>5.178600000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.993099999999999</v>
+        <v>-1.9933</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3658000000000001</v>
+        <v>0.3658000000000019</v>
       </c>
       <c r="H16" t="n">
         <v>6.456200000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-6.090599999999999</v>
+        <v>-6.0906</v>
       </c>
       <c r="J16" t="n">
         <v>7.696099999999999</v>
@@ -1702,13 +1702,13 @@
         <v>14.6606</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9162999999999998</v>
+        <v>-0.6409000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.116</v>
+        <v>-0.8406</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1995</v>
+        <v>0.1996</v>
       </c>
       <c r="V16" t="n">
         <v>2.544400000000001</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. YURCHENKO</t>
+          <t>P. VILLAGRASA TORTAJADA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.8897</v>
+        <v>3.8817</v>
       </c>
       <c r="E17" t="n">
-        <v>5.1966</v>
+        <v>3.0188</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3069</v>
+        <v>0.8629</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5116000000000001</v>
+        <v>2.8135</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.515</v>
+        <v>0.9897</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0034</v>
+        <v>1.8238</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1741</v>
+        <v>3.1617</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6692</v>
+        <v>1.7865</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8433</v>
+        <v>1.3753</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6857</v>
+        <v>-0.3483</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8457</v>
+        <v>-0.7968</v>
       </c>
       <c r="O17" t="n">
-        <v>0.16</v>
+        <v>0.4486</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1991</v>
+        <v>0.733</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1991</v>
+        <v>0.733</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1918</v>
+        <v>0.3352</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1116</v>
+        <v>-0.1429</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0801</v>
+        <v>0.4781</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.9109</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.9005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. VILLAGRASA TORTAJADA</t>
+          <t>S. YURCHENKO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.4383</v>
+        <v>3.1721</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3073</v>
+        <v>3.1774</v>
       </c>
       <c r="F18" t="n">
-        <v>1.131</v>
+        <v>-0.0053</v>
       </c>
       <c r="G18" t="n">
-        <v>2.8135</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9897</v>
+        <v>-1.515</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8238</v>
+        <v>1.0034</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1617</v>
+        <v>0.1741</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7865</v>
+        <v>-0.6692</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3753</v>
+        <v>0.8433</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3483</v>
+        <v>-0.6857</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7968</v>
+        <v>-0.8457</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4486</v>
+        <v>0.16</v>
       </c>
       <c r="P18" t="n">
-        <v>0.733</v>
+        <v>2.1991</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.733</v>
+        <v>2.1991</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8918</v>
+        <v>1.4742</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1456</v>
+        <v>1.0924</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7463</v>
+        <v>0.3818</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.9109</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7355</v>
+        <v>0.6685</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2735</v>
+        <v>0.1773</v>
       </c>
       <c r="F19" t="n">
-        <v>0.462</v>
+        <v>0.4911</v>
       </c>
       <c r="G19" t="n">
         <v>1.527</v>
@@ -1936,13 +1936,13 @@
         <v>2.1991</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9295</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5475</v>
+        <v>0.4514</v>
       </c>
       <c r="U19" t="n">
-        <v>0.449</v>
+        <v>0.4781</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3219</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2036</v>
+        <v>0.4637</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3998</v>
+        <v>1.5921</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6035</v>
+        <v>-1.1285</v>
       </c>
       <c r="G20" t="n">
         <v>-1.272</v>
@@ -2014,13 +2014,13 @@
         <v>0.5498</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3819</v>
+        <v>-0.7146</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7157</v>
+        <v>-0.5234</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6662</v>
+        <v>-0.1912</v>
       </c>
       <c r="V20" t="n">
         <v>1.9005</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3834</v>
+        <v>0.1994</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2733</v>
+        <v>0.1113</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1101</v>
+        <v>0.0881</v>
       </c>
       <c r="G21" t="n">
         <v>0.0531</v>
@@ -2092,13 +2092,13 @@
         <v>0.9163</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4365</v>
+        <v>0.1463</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2391</v>
+        <v>0.1456</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1974</v>
+        <v>0.0007</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2378</v>
+        <v>-0.9232</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0694</v>
+        <v>0.4541</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3073</v>
+        <v>-1.3773</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8078</v>
@@ -2170,13 +2170,13 @@
         <v>2.0158</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0881</v>
+        <v>0.4027</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3137</v>
+        <v>0.0709</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4018</v>
+        <v>0.3318</v>
       </c>
       <c r="V22" t="n">
         <v>-2.5339</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4734</v>
+        <v>-0.9503</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0035</v>
+        <v>-0.8112</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4699</v>
+        <v>-0.1391</v>
       </c>
       <c r="G23" t="n">
         <v>0.6889</v>
@@ -2248,13 +2248,13 @@
         <v>1.8326</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5734</v>
+        <v>-0.0503</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.3778</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0033</v>
+        <v>0.3275</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5889</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9251</v>
+        <v>-2.0422</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8937</v>
+        <v>-2.3168</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0313</v>
+        <v>0.2746</v>
       </c>
       <c r="G24" t="n">
         <v>-0.495</v>
@@ -2326,13 +2326,13 @@
         <v>1.8326</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2309</v>
+        <v>-0.348</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.138</v>
+        <v>-0.5611</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0929</v>
+        <v>0.213</v>
       </c>
       <c r="V24" t="n">
         <v>0.6335</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. DE LA CAL DOMINGUEZ</t>
+          <t>H. GOMEZ GARCIA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.306</v>
+        <v>-2.9388</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.9626</v>
+        <v>-2.6396</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3434</v>
+        <v>-0.2992</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.1286</v>
+        <v>-1.2332</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7568</v>
+        <v>-0.5183</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3719</v>
+        <v>-0.7148</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0584</v>
+        <v>-0.0042</v>
       </c>
       <c r="K25" t="n">
-        <v>0.4736</v>
+        <v>0.486</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5319</v>
+        <v>-0.4902</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.0703</v>
+        <v>-1.229</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.2303</v>
+        <v>-1.0044</v>
       </c>
       <c r="O25" t="n">
-        <v>0.16</v>
+        <v>-0.2246</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.2828</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.8326</v>
+        <v>-2.7489</v>
       </c>
       <c r="R25" t="n">
-        <v>0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5726</v>
+        <v>0.4489</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6606</v>
+        <v>0.1135</v>
       </c>
       <c r="U25" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.3354</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3219</v>
       </c>
       <c r="W25" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.9109</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>H. GOMEZ GARCIA</t>
+          <t>A. DE LA CAL DOMINGUEZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.4443</v>
+        <v>-3.1589</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.1203</v>
+        <v>-0.7703</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.324</v>
+        <v>-2.3886</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.2332</v>
+        <v>-1.1286</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.5183</v>
+        <v>-0.7568</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7148</v>
+        <v>-0.3719</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0042</v>
+        <v>-0.0584</v>
       </c>
       <c r="K26" t="n">
-        <v>0.486</v>
+        <v>0.4736</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.4902</v>
+        <v>-0.5319</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.229</v>
+        <v>-1.0703</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.0044</v>
+        <v>-1.2303</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.2246</v>
+        <v>0.16</v>
       </c>
       <c r="P26" t="n">
+        <v>-1.2828</v>
+      </c>
+      <c r="Q26" t="n">
         <v>-1.8326</v>
       </c>
-      <c r="Q26" t="n">
-        <v>-2.7489</v>
-      </c>
       <c r="R26" t="n">
-        <v>0.9163</v>
+        <v>0.5498</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.0566</v>
+        <v>-0.4255</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3673</v>
+        <v>-0.4683</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3106</v>
+        <v>0.0428</v>
       </c>
       <c r="V26" t="n">
         <v>-0.3219</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.3219</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.910100000000001</v>
+        <v>-1.628</v>
       </c>
       <c r="E27" t="n">
-        <v>1.993199999999999</v>
+        <v>1.9931</v>
       </c>
       <c r="F27" t="n">
-        <v>-4.9034</v>
+        <v>-3.6213</v>
       </c>
       <c r="G27" t="n">
         <v>-0.3657000000000004</v>
@@ -2539,10 +2539,10 @@
         <v>3.4812</v>
       </c>
       <c r="L27" t="n">
-        <v>3.8492</v>
+        <v>3.849200000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>-7.6963</v>
+        <v>-7.696300000000001</v>
       </c>
       <c r="N27" t="n">
         <v>-9.9375</v>
@@ -2560,13 +2560,13 @@
         <v>13.7444</v>
       </c>
       <c r="S27" t="n">
-        <v>0.916300000000001</v>
+        <v>2.1984</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.1997999999999999</v>
+        <v>-0.1997</v>
       </c>
       <c r="U27" t="n">
-        <v>1.116</v>
+        <v>2.398</v>
       </c>
       <c r="V27" t="n">
         <v>-2.5441</v>
